--- a/Project Outputs for UltraZohm Analog Fast ADC 1v01 ADS5272 3U/BOM/BOM_Analog_Daugther_MAX11331_6U_1v02_1v02.xlsx
+++ b/Project Outputs for UltraZohm Analog Fast ADC 1v01 ADS5272 3U/BOM/BOM_Analog_Daugther_MAX11331_6U_1v02_1v02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thoma\Documents\Altium\UltraZOhm\Slow ADC Adapter\Project Outputs for UltraZohm Analog Fast ADC 1v01 ADS5272 3U\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{99EEB995-13E5-4DBF-8AFE-F365AF2C2859}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{24618F72-5E90-4587-B9E8-85C3C424A0E7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11385" xr2:uid="{F0B5CDE6-A794-415D-B60A-DA8FB42A6B86}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11385" xr2:uid="{8FCC0902-37EF-4F14-B3BE-B08296339777}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM_Analog_Daugther_MAX11331_6U" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,9 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -34,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="216">
   <si>
     <t>Quantity</t>
   </si>
@@ -93,276 +95,432 @@
     <t>BS1, BS2, BS3</t>
   </si>
   <si>
+    <t>Stackpole Electronics</t>
+  </si>
+  <si>
     <t>6A</t>
   </si>
   <si>
     <t>RES_1206</t>
   </si>
   <si>
+    <t>Digikey</t>
+  </si>
+  <si>
+    <t>RMCF1206ZT0R00CT-ND</t>
+  </si>
+  <si>
+    <t>200pF</t>
+  </si>
+  <si>
+    <t>C2A, C2B, C2C, C2D, C2E, C2F, C2G, C2H, C5A, C5B, C5C, C5D, C5E, C5F, C5G, C5H, C6A, C6B, C6C, C6D, C6E, C6F, C6G, C6H, C9A, C9B, C9C, C9D, C9E, C9F, C9G, C9H, C10A, C10B, C10C, C10D, C10E, C10F, C10G, C10H, C13A, C13B, C13C, C13D, C13E, C13F, C13G, C13H, C18A, C18B, C18C, C18D, C18E, C18F, C18G, C18H, C21A, C21B, C21C, C21D, C21E, C21F, C21G, C21H</t>
+  </si>
+  <si>
+    <t>Walsin</t>
+  </si>
+  <si>
+    <t>0603N201J500CT</t>
+  </si>
+  <si>
+    <t>Capacitor</t>
+  </si>
+  <si>
+    <t>CAP_0603</t>
+  </si>
+  <si>
+    <t>1292-1499-1-ND</t>
+  </si>
+  <si>
     <t>100pF</t>
   </si>
   <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>Capacitor</t>
-  </si>
-  <si>
-    <t>Cap_1210</t>
-  </si>
-  <si>
-    <t>1000V</t>
-  </si>
-  <si>
-    <t>200pF</t>
-  </si>
-  <si>
-    <t>C2A, C2B, C2C, C2D, C2E, C2F, C2G, C2H, C5A, C5B, C5C, C5D, C5E, C5F, C5G, C5H, C6A, C6B, C6C, C6D, C6E, C6F, C6G, C6H, C9A, C9B, C9C, C9D, C9E, C9F, C9G, C9H, C10A, C10B, C10C, C10D, C10E, C10F, C10G, C10H, C13A, C13B, C13C, C13D, C13E, C13F, C13G, C13H, C18A, C18B, C18C, C18D, C18E, C18F, C18G, C18H, C21A, C21B, C21C, C21D, C21E, C21F, C21G, C21H</t>
-  </si>
-  <si>
-    <t>CAP_0603</t>
-  </si>
-  <si>
     <t>C3A, C3B, C3C, C3D, C3E, C3F, C3G, C3H, C7A, C7B, C7C, C7D, C7E, C7F, C7G, C7H, C11A, C11B, C11C, C11D, C11E, C11F, C11G, C11H, C19A, C19B, C19C, C19D, C19E, C19F, C19G, C19H</t>
   </si>
   <si>
+    <t>Würth Elektronik</t>
+  </si>
+  <si>
+    <t>885012006023</t>
+  </si>
+  <si>
+    <t>732-7766-1-ND</t>
+  </si>
+  <si>
     <t>100nF</t>
   </si>
   <si>
     <t>C4A, C4B, C4C, C4D, C4E, C4F, C4G, C4H, C8A, C8B, C8C, C8D, C8E, C8F, C8G, C8H, C12A, C12B, C12C, C12D, C12E, C12F, C12G, C12H, C20A, C20B, C20C, C20D, C20E, C20F, C20G, C20H</t>
   </si>
   <si>
+    <t>Samsung</t>
+  </si>
+  <si>
+    <t>CL31B105KOFNNNE</t>
+  </si>
+  <si>
+    <t>16V</t>
+  </si>
+  <si>
+    <t>1276-1783-1-ND</t>
+  </si>
+  <si>
+    <t>C14A, C14B, C14C, C14D, C14E, C14F, C14G, C14H, C15A, C15B, C15C, C15D, C15E, C15F, C15G, C15H, C16A, C16B, C16C, C16D, C16E, C16F, C16G, C16H, C17A, C17B, C17C, C17D, C17E, C17F, C17G, C17H, C22A, C22B, C22C, C22D, C22E, C22F, C22G, C22H, C23A, C23B, C23C, C23D, C23E, C23F, C23G, C23H, C24A, C24B, C24C, C24D, C24E, C24F, C24G, C24H, C25A, C25B, C25C, C25D, C25E, C25F, C25G, C25H, C27A, C27B, C27C, C27D, C28A, C28B, C28C, C28D, C30A, C30B, C30C, C30D, C34A, C34B, C34C, C34D, C35, C36, C38, C39, C40, C45, C48</t>
+  </si>
+  <si>
+    <t>CL10B104KA8NNNC</t>
+  </si>
+  <si>
+    <t>1276-1006-1-ND</t>
+  </si>
+  <si>
+    <t>10uF</t>
+  </si>
+  <si>
+    <t>C26A, C26B, C26C, C26D, C33A, C33B, C33C, C33D</t>
+  </si>
+  <si>
+    <t>Tayo Yuden</t>
+  </si>
+  <si>
+    <t>JMK107ABJ106MA-T</t>
+  </si>
+  <si>
+    <t>Capacitor Ceramic</t>
+  </si>
+  <si>
+    <t>6.3V</t>
+  </si>
+  <si>
+    <t>587-5869-1-ND</t>
+  </si>
+  <si>
+    <t>470nF</t>
+  </si>
+  <si>
+    <t>C31A, C31B, C31C, C31D, C32A, C32B, C32C, C32D</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 885012206006</t>
+  </si>
+  <si>
+    <t>10V</t>
+  </si>
+  <si>
+    <t>732-7925-1-ND</t>
+  </si>
+  <si>
+    <t>2.2nF</t>
+  </si>
+  <si>
+    <t>C41</t>
+  </si>
+  <si>
+    <t>KEMET</t>
+  </si>
+  <si>
+    <t>C0603C222K5RACTU</t>
+  </si>
+  <si>
+    <t>50V</t>
+  </si>
+  <si>
+    <t>399-1085-1-ND</t>
+  </si>
+  <si>
+    <t>1.2nF</t>
+  </si>
+  <si>
+    <t>C42</t>
+  </si>
+  <si>
+    <t>Murata</t>
+  </si>
+  <si>
+    <t>GRM1885C1H122JA01D</t>
+  </si>
+  <si>
+    <t>490-1453-1-ND</t>
+  </si>
+  <si>
+    <t>68µF</t>
+  </si>
+  <si>
+    <t>C43, C44</t>
+  </si>
+  <si>
+    <t>WCAP-ATG8 THT Aluminum Electrolytic Capacitors, D6.3mm x L11mm, 68uF, +/-20%, 35VDC</t>
+  </si>
+  <si>
+    <t>WCAP-ATG8_6.3x11</t>
+  </si>
+  <si>
+    <t>732-8736-1-ND</t>
+  </si>
+  <si>
+    <t>10µF</t>
+  </si>
+  <si>
+    <t>C46, C47</t>
+  </si>
+  <si>
+    <t>CL31A106MBHNNNE</t>
+  </si>
+  <si>
+    <t>35 V</t>
+  </si>
+  <si>
+    <t>1276-6736-1-ND</t>
+  </si>
+  <si>
+    <t>1µF</t>
+  </si>
+  <si>
+    <t>C49</t>
+  </si>
+  <si>
+    <t>CL10A105KB8NNNC</t>
+  </si>
+  <si>
+    <t>50 V</t>
+  </si>
+  <si>
+    <t>1276-1860-1-ND</t>
+  </si>
+  <si>
+    <t>91pF</t>
+  </si>
+  <si>
+    <t>C50</t>
+  </si>
+  <si>
+    <t>GRM1885C1H910JA01D</t>
+  </si>
+  <si>
+    <t>490-1426-1-ND</t>
+  </si>
+  <si>
+    <t>VCC</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>150080BS75000</t>
+  </si>
+  <si>
+    <t>LED Blue</t>
+  </si>
+  <si>
+    <t>LED_0805_GREEN</t>
+  </si>
+  <si>
+    <t>732-4982-1-ND</t>
+  </si>
+  <si>
+    <t>VIN</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>Conector RJ-45 4x2</t>
+  </si>
+  <si>
+    <t>J1</t>
+  </si>
+  <si>
+    <t>TE Connectivity</t>
+  </si>
+  <si>
+    <t>1-1734715-2</t>
+  </si>
+  <si>
+    <t>RJ45 - 4x2</t>
+  </si>
+  <si>
+    <t>A118195-ND</t>
+  </si>
+  <si>
+    <t>33µH</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>Taiyo Yuden</t>
+  </si>
+  <si>
+    <t>NRS5030T330MMGJ</t>
+  </si>
+  <si>
+    <t>SMT power Inductor, 33µH, 225m DRC</t>
+  </si>
+  <si>
+    <t>Inductor 5030</t>
+  </si>
+  <si>
+    <t>587-3458-1-ND</t>
+  </si>
+  <si>
+    <t>10k</t>
+  </si>
+  <si>
+    <t>R2A, R2B, R2C, R2D, R2E, R2F, R2G, R2H, R13A, R13B, R13C, R13D, R13E, R13F, R13G, R13H</t>
+  </si>
+  <si>
+    <t>Vishay</t>
+  </si>
+  <si>
+    <t>ACASA1002S1002P100</t>
+  </si>
+  <si>
+    <t>Chip Resistor Array 0606, 4xR</t>
+  </si>
+  <si>
+    <t>CAC-80P320X160-8N</t>
+  </si>
+  <si>
+    <t>749-1023-1-ND</t>
+  </si>
+  <si>
+    <t>48.7</t>
+  </si>
+  <si>
+    <t>R3A, R3B, R3C, R3D, R3E, R3F, R3G, R3H, R6A, R6B, R6C, R6D, R6E, R6F, R6G, R6H, R8A, R8B, R8C, R8D, R8E, R8F, R8G, R8H, R11A, R11B, R11C, R11D, R11E, R11F, R11G, R11H, R14A, R14B, R14C, R14D, R14E, R14F, R14G, R14H, R17A, R17B, R17C, R17D, R17E, R17F, R17G, R17H, R19A, R19B, R19C, R19D, R19E, R19F, R19G, R19H, R22A, R22B, R22C, R22D, R22E, R22F, R22G, R22H</t>
+  </si>
+  <si>
+    <t>Panasonic</t>
+  </si>
+  <si>
+    <t>ERA-3AEB48R7V</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>C14A, C14B, C14C, C14D, C14E, C14F, C14G, C14H, C15A, C15B, C15C, C15D, C15E, C15F, C15G, C15H, C16A, C16B, C16C, C16D, C16E, C16F, C16G, C16H, C17A, C17B, C17C, C17D, C17E, C17F, C17G, C17H, C22A, C22B, C22C, C22D, C22E, C22F, C22G, C22H, C23A, C23B, C23C, C23D, C23E, C23F, C23G, C23H, C24A, C24B, C24C, C24D, C24E, C24F, C24G, C24H, C25A, C25B, C25C, C25D, C25E, C25F, C25G, C25H, C27A, C27B, C27C, C27D, C28A, C28B, C28C, C28D, C30A, C30B, C30C, C30D, C34A, C34B, C34C, C34D, C35, C36, C38, C39, C40, C45, C48</t>
-  </si>
-  <si>
-    <t>10uF</t>
-  </si>
-  <si>
-    <t>C26A, C26B, C26C, C26D, C33A, C33B, C33C, C33D</t>
-  </si>
-  <si>
-    <t>Capacitor Ceramic</t>
-  </si>
-  <si>
-    <t>10V</t>
-  </si>
-  <si>
-    <t>470nF</t>
-  </si>
-  <si>
-    <t>C31A, C31B, C31C, C31D, C32A, C32B, C32C, C32D</t>
-  </si>
-  <si>
-    <t>2.2nF</t>
-  </si>
-  <si>
-    <t>C41</t>
-  </si>
-  <si>
-    <t>50V</t>
-  </si>
-  <si>
-    <t>1.2nF</t>
-  </si>
-  <si>
-    <t>C42</t>
-  </si>
-  <si>
-    <t>68µF</t>
-  </si>
-  <si>
-    <t>C43, C44</t>
-  </si>
-  <si>
-    <t>WCAP-ATG8 THT Aluminum Electrolytic Capacitors, D6.3mm x L11mm, 68uF, +/-20%, 35VDC</t>
-  </si>
-  <si>
-    <t>WCAP-ATG8_6.3x11</t>
-  </si>
-  <si>
-    <t>Digikey</t>
-  </si>
-  <si>
-    <t>732-8736-1-ND</t>
-  </si>
-  <si>
-    <t>10µF</t>
-  </si>
-  <si>
-    <t>C46, C47</t>
-  </si>
-  <si>
-    <t>35 V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  1µF</t>
-  </si>
-  <si>
-    <t>C49</t>
-  </si>
-  <si>
-    <t>50 V</t>
-  </si>
-  <si>
-    <t>91pF</t>
-  </si>
-  <si>
-    <t>C50</t>
-  </si>
-  <si>
-    <t>VCC</t>
-  </si>
-  <si>
-    <t>D1</t>
-  </si>
-  <si>
-    <t>LED Blue</t>
-  </si>
-  <si>
-    <t>LED_0805_GREEN</t>
-  </si>
-  <si>
-    <t>VIN</t>
-  </si>
-  <si>
-    <t>D2</t>
-  </si>
-  <si>
-    <t>Conector RJ-45 4x2</t>
-  </si>
-  <si>
-    <t>J1</t>
-  </si>
-  <si>
-    <t>RJ45 - 4x2</t>
-  </si>
-  <si>
-    <t>33µH</t>
-  </si>
-  <si>
-    <t>L1</t>
-  </si>
-  <si>
-    <t>Taiyo Yuden</t>
-  </si>
-  <si>
-    <t>NRS5030T330MMGJ</t>
-  </si>
-  <si>
-    <t>SMT power Inductor, 33µH, 225m DRC</t>
-  </si>
-  <si>
-    <t>Inductor 5030</t>
-  </si>
-  <si>
-    <t>587-3458-1-ND</t>
-  </si>
-  <si>
-    <t>MH_3mm</t>
-  </si>
-  <si>
-    <t>MH1, MH2</t>
-  </si>
-  <si>
-    <t>Mounting Hole</t>
-  </si>
-  <si>
-    <t>1M</t>
-  </si>
-  <si>
-    <t>R1</t>
-  </si>
-  <si>
-    <t>Resistor</t>
-  </si>
-  <si>
-    <t>10k</t>
-  </si>
-  <si>
-    <t>R2A, R2B, R2C, R2D, R2E, R2F, R2G, R2H, R13A, R13B, R13C, R13D, R13E, R13F, R13G, R13H</t>
-  </si>
-  <si>
-    <t>Vishay</t>
-  </si>
-  <si>
-    <t>ACASA1002S1002P100</t>
-  </si>
-  <si>
-    <t>Chip Resistor Array 0606, 4xR</t>
-  </si>
-  <si>
-    <t>CAC-80P320X160-8N</t>
-  </si>
-  <si>
-    <t>749-1023-1-ND</t>
-  </si>
-  <si>
-    <t>48.7</t>
-  </si>
-  <si>
-    <t>R3A, R3B, R3C, R3D, R3E, R3F, R3G, R3H, R6A, R6B, R6C, R6D, R6E, R6F, R6G, R6H, R8A, R8B, R8C, R8D, R8E, R8F, R8G, R8H, R11A, R11B, R11C, R11D, R11E, R11F, R11G, R11H, R14A, R14B, R14C, R14D, R14E, R14F, R14G, R14H, R17A, R17B, R17C, R17D, R17E, R17F, R17G, R17H, R19A, R19B, R19C, R19D, R19E, R19F, R19G, R19H, R22A, R22B, R22C, R22D, R22E, R22F, R22G, R22H</t>
-  </si>
-  <si>
     <t>RES_0603</t>
   </si>
   <si>
+    <t>P48.7DBCT-ND</t>
+  </si>
+  <si>
     <t>24.3k</t>
   </si>
   <si>
     <t>R4A, R4B, R4C, R4D, R4E, R4F, R4G, R4H, R7A, R7B, R7C, R7D, R7E, R7F, R7G, R7H, R9A, R9B, R9C, R9D, R9E, R9F, R9G, R9H, R12A, R12B, R12C, R12D, R12E, R12F, R12G, R12H, R15A, R15B, R15C, R15D, R15E, R15F, R15G, R15H, R18A, R18B, R18C, R18D, R18E, R18F, R18G, R18H, R20A, R20B, R20C, R20D, R20E, R20F, R20G, R20H, R23A, R23B, R23C, R23D, R23E, R23F, R23G, R23H</t>
   </si>
   <si>
-    <t>160</t>
+    <t>ERJ-PB3B2432V</t>
+  </si>
+  <si>
+    <t>P20128CT-ND</t>
+  </si>
+  <si>
+    <t>160R</t>
   </si>
   <si>
     <t>R5A, R5B, R5C, R5D, R5E, R5F, R5G, R5H, R10A, R10B, R10C, R10D, R10E, R10F, R10G, R10H, R16A, R16B, R16C, R16D, R16E, R16F, R16G, R16H, R21A, R21B, R21C, R21D, R21E, R21F, R21G, R21H</t>
   </si>
   <si>
+    <t>Yageo</t>
+  </si>
+  <si>
+    <t>RC1206FR-07160RL</t>
+  </si>
+  <si>
     <t>Limiter Resistor</t>
   </si>
   <si>
+    <t>311-160FRCT-ND</t>
+  </si>
+  <si>
     <t>100R</t>
   </si>
   <si>
     <t>R25, R26, R27, R37</t>
   </si>
   <si>
+    <t>RC0603FR-07100RL</t>
+  </si>
+  <si>
+    <t>311-100HRCT-ND</t>
+  </si>
+  <si>
     <t>R28, R29, R30, R34</t>
   </si>
   <si>
+    <t>RC0603FR-0710KL</t>
+  </si>
+  <si>
+    <t>311-10.0KHRCT-ND</t>
+  </si>
+  <si>
     <t>2.2M</t>
   </si>
   <si>
     <t>R31</t>
   </si>
   <si>
+    <t>KOA Speer</t>
+  </si>
+  <si>
+    <t>RK73H1JTTD2204F</t>
+  </si>
+  <si>
+    <t>2019-RK73H1JTTD2204FCT-ND</t>
+  </si>
+  <si>
     <t>200k</t>
   </si>
   <si>
     <t>R32</t>
   </si>
   <si>
+    <t>ERJ-3EKF2003V</t>
+  </si>
+  <si>
+    <t>P200KHCT-ND</t>
+  </si>
+  <si>
     <t>115k</t>
   </si>
   <si>
     <t>R33</t>
   </si>
   <si>
+    <t>RK73H1JTTD1153F</t>
+  </si>
+  <si>
+    <t>2019-RK73H1JTTD1153FCT-ND</t>
+  </si>
+  <si>
     <t>100k</t>
   </si>
   <si>
     <t>R35</t>
   </si>
   <si>
+    <t>Susumu</t>
+  </si>
+  <si>
+    <t>RR0816P-104-D</t>
+  </si>
+  <si>
+    <t>RR08P100KDCT-ND</t>
+  </si>
+  <si>
     <t>330</t>
   </si>
   <si>
     <t>R36</t>
   </si>
   <si>
+    <t>RC0603FR-07330RL</t>
+  </si>
+  <si>
+    <t>311-330HRCT-ND</t>
+  </si>
+  <si>
     <t>20k</t>
   </si>
   <si>
@@ -375,94 +533,16 @@
     <t>REF1A, REF1B, REF1C, REF1D</t>
   </si>
   <si>
+    <t>Texas Instruments</t>
+  </si>
+  <si>
+    <t>REF2033AIDDCT</t>
+  </si>
+  <si>
     <t>SOT-23-5</t>
   </si>
   <si>
-    <t>TP1</t>
-  </si>
-  <si>
-    <t>Keystone Electronics</t>
-  </si>
-  <si>
-    <t>5006</t>
-  </si>
-  <si>
-    <t>1.6mm Test Point Keystone</t>
-  </si>
-  <si>
-    <t>TP_1.6mm</t>
-  </si>
-  <si>
-    <t>36-5006-ND</t>
-  </si>
-  <si>
-    <t>TP2</t>
-  </si>
-  <si>
-    <t>DGND</t>
-  </si>
-  <si>
-    <t>TP3</t>
-  </si>
-  <si>
-    <t>GND</t>
-  </si>
-  <si>
-    <t>TP4</t>
-  </si>
-  <si>
-    <t>AGND</t>
-  </si>
-  <si>
-    <t>TP5</t>
-  </si>
-  <si>
-    <t>SCLK</t>
-  </si>
-  <si>
-    <t>TP6</t>
-  </si>
-  <si>
-    <t>SCLKRTN</t>
-  </si>
-  <si>
-    <t>TP7</t>
-  </si>
-  <si>
-    <t>MISO1</t>
-  </si>
-  <si>
-    <t>TP8</t>
-  </si>
-  <si>
-    <t>MISO2</t>
-  </si>
-  <si>
-    <t>TP9</t>
-  </si>
-  <si>
-    <t>MISO3</t>
-  </si>
-  <si>
-    <t>TP10</t>
-  </si>
-  <si>
-    <t>MOSI</t>
-  </si>
-  <si>
-    <t>TP11</t>
-  </si>
-  <si>
-    <t>MISO4</t>
-  </si>
-  <si>
-    <t>TP12</t>
-  </si>
-  <si>
-    <t>CS</t>
-  </si>
-  <si>
-    <t>TP13</t>
+    <t>296-40487-1-ND</t>
   </si>
   <si>
     <t>THS4524</t>
@@ -471,9 +551,6 @@
     <t>U1A, U1B, U1C, U1D, U1E, U1F, U1G, U1H</t>
   </si>
   <si>
-    <t>Texas Instruments</t>
-  </si>
-  <si>
     <t>Quad Channel fully differential Amplilfier</t>
   </si>
   <si>
@@ -483,10 +560,7 @@
     <t>TSSOP-38</t>
   </si>
   <si>
-    <t>Mouser</t>
-  </si>
-  <si>
-    <t>595-THS4524IDBTR</t>
+    <t>296-24315-1-ND</t>
   </si>
   <si>
     <t>MAX11331</t>
@@ -495,12 +569,21 @@
     <t>U2A, U2B, U2C, U2D</t>
   </si>
   <si>
+    <t>Maximm Integrated</t>
+  </si>
+  <si>
+    <t>MAX11331ATJ+</t>
+  </si>
+  <si>
     <t>ADC 12 bits SPI</t>
   </si>
   <si>
     <t>32-TQFN-EP (5x5)</t>
   </si>
   <si>
+    <t>MAX11331ATJ+-ND</t>
+  </si>
+  <si>
     <t>Quad LVDS reciever</t>
   </si>
   <si>
@@ -570,7 +653,7 @@
     <t>SOIC127P600X170_HS-9N</t>
   </si>
   <si>
-    <t>296-LM5163DDARCT-ND*</t>
+    <t>296-LM5163DDARCT-ND</t>
   </si>
   <si>
     <t>IPL1-102-01-L-D-K</t>
@@ -579,16 +662,19 @@
     <t>X1</t>
   </si>
   <si>
+    <t>Samtec</t>
+  </si>
+  <si>
     <t>2.54mm Double Row Terminal Assembly, Right-Angled</t>
   </si>
   <si>
+    <t>SAM10565-ND</t>
+  </si>
+  <si>
     <t>2x8 Pin</t>
   </si>
   <si>
     <t>X2</t>
-  </si>
-  <si>
-    <t>Samtec</t>
   </si>
   <si>
     <t>EHF-108-01-F-D</t>
@@ -979,11 +1065,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C6F73E8-189F-48A3-938E-D4F17CFB251F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A4CB069-BA8E-42EA-B2F9-38F8021529E7}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q55"/>
+  <dimension ref="A1:Q39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -1056,7 +1142,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>3</v>
       </c>
@@ -1066,84 +1152,104 @@
       <c r="C2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="3"/>
+      <c r="D2" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
+      <c r="L2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="315" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="F3" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I3" s="3"/>
-      <c r="J3" s="4" t="s">
-        <v>25</v>
-      </c>
+      <c r="J3" s="3"/>
       <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
+      <c r="L3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>30</v>
+      </c>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
     </row>
-    <row r="4" spans="1:17" ht="315" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="165" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
+        <v>32</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="F4" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
+      <c r="L4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
@@ -1154,91 +1260,117 @@
         <v>32</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>28</v>
-      </c>
       <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
+      <c r="J5" s="4" t="s">
+        <v>40</v>
+      </c>
       <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
+      <c r="L5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
     </row>
-    <row r="6" spans="1:17" ht="165" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <v>32</v>
+        <v>87</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="F6" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I6" s="3"/>
-      <c r="J6" s="4" t="s">
-        <v>32</v>
-      </c>
+      <c r="J6" s="3"/>
       <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
+      <c r="L6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
     </row>
-    <row r="7" spans="1:17" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>87</v>
+        <v>8</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
+        <v>46</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="F7" s="4" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
+      <c r="J7" s="4" t="s">
+        <v>50</v>
+      </c>
       <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
+      <c r="L7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>51</v>
+      </c>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
@@ -1249,62 +1381,78 @@
         <v>8</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
+        <v>53</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="F8" s="4" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="4" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
+      <c r="L8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>56</v>
+      </c>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
     </row>
-    <row r="9" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>60</v>
+      </c>
       <c r="F9" s="4" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="4" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
+      <c r="L9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
@@ -1315,130 +1463,154 @@
         <v>1</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
+        <v>64</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="F10" s="4" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="4" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
+      <c r="L10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>67</v>
+      </c>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
     </row>
-    <row r="11" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" ht="135" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="4" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="I11" s="3"/>
-      <c r="J11" s="4" t="s">
-        <v>42</v>
-      </c>
+      <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
+      <c r="L11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>72</v>
+      </c>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
     </row>
-    <row r="12" spans="1:17" ht="135" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>2</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
+        <v>74</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>75</v>
+      </c>
       <c r="F12" s="4" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
+      <c r="J12" s="4" t="s">
+        <v>76</v>
+      </c>
       <c r="K12" s="3"/>
       <c r="L12" s="4" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
+        <v>79</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>80</v>
+      </c>
       <c r="F13" s="4" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="4" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
+      <c r="L13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>82</v>
+      </c>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
@@ -1449,29 +1621,37 @@
         <v>1</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
+        <v>84</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>85</v>
+      </c>
       <c r="F14" s="4" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
+      <c r="L14" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>86</v>
+      </c>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
@@ -1482,29 +1662,33 @@
         <v>1</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F15" s="3"/>
       <c r="G15" s="4" t="s">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>28</v>
+        <v>91</v>
       </c>
       <c r="I15" s="3"/>
-      <c r="J15" s="4" t="s">
-        <v>42</v>
-      </c>
+      <c r="J15" s="3"/>
       <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
+      <c r="L15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>92</v>
+      </c>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
@@ -1515,25 +1699,33 @@
         <v>1</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>89</v>
+      </c>
       <c r="F16" s="3"/>
       <c r="G16" s="4" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
+      <c r="L16" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>92</v>
+      </c>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
@@ -1544,285 +1736,345 @@
         <v>1</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
+        <v>96</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>98</v>
+      </c>
       <c r="F17" s="3"/>
       <c r="G17" s="4" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
+      <c r="L17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>100</v>
+      </c>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
     </row>
-    <row r="18" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>1</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
+        <v>102</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>101</v>
+      </c>
       <c r="G18" s="4" t="s">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>67</v>
+        <v>106</v>
       </c>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
+      <c r="L18" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>107</v>
+      </c>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
     </row>
-    <row r="19" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>69</v>
+        <v>109</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="4" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
     </row>
-    <row r="20" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" ht="315" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
+        <v>116</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>115</v>
+      </c>
       <c r="G20" s="4" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
+      <c r="L20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>121</v>
+      </c>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="315" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
+        <v>123</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>124</v>
+      </c>
       <c r="F21" s="4" t="s">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
+      <c r="L21" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>125</v>
+      </c>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
     </row>
-    <row r="22" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" ht="165" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>83</v>
+        <v>128</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
       <c r="L22" s="4" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>87</v>
+        <v>131</v>
       </c>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
     </row>
-    <row r="23" spans="1:17" ht="315" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
+        <v>133</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>134</v>
+      </c>
       <c r="F23" s="4" t="s">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
+      <c r="L23" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>135</v>
+      </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
     </row>
-    <row r="24" spans="1:17" ht="315" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
+        <v>136</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>137</v>
+      </c>
       <c r="F24" s="4" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
+      <c r="L24" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>138</v>
+      </c>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
     </row>
-    <row r="25" spans="1:17" ht="165" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>93</v>
+        <v>139</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
+        <v>140</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>142</v>
+      </c>
       <c r="F25" s="4" t="s">
-        <v>93</v>
+        <v>139</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
+      <c r="L25" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>143</v>
+      </c>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
@@ -1830,92 +2082,116 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>96</v>
+        <v>144</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
+        <v>145</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>146</v>
+      </c>
       <c r="F26" s="4" t="s">
-        <v>96</v>
+        <v>144</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
+      <c r="L26" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>147</v>
+      </c>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
+        <v>149</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>150</v>
+      </c>
       <c r="F27" s="4" t="s">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
+      <c r="L27" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M27" s="4" t="s">
+        <v>151</v>
+      </c>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>1</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>99</v>
+        <v>152</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
+        <v>153</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>155</v>
+      </c>
       <c r="F28" s="4" t="s">
-        <v>99</v>
+        <v>152</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
+      <c r="L28" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M28" s="4" t="s">
+        <v>156</v>
+      </c>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
@@ -1926,27 +2202,35 @@
         <v>1</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>101</v>
+        <v>157</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
+        <v>158</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>159</v>
+      </c>
       <c r="F29" s="4" t="s">
-        <v>101</v>
+        <v>157</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
+      <c r="L29" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M29" s="4" t="s">
+        <v>160</v>
+      </c>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
@@ -1957,924 +2241,380 @@
         <v>1</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>103</v>
+        <v>161</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
+        <v>162</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>159</v>
+      </c>
       <c r="F30" s="4" t="s">
-        <v>103</v>
+        <v>161</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
+      <c r="L30" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M30" s="4" t="s">
+        <v>160</v>
+      </c>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>105</v>
+        <v>163</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="4" t="s">
-        <v>105</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="F31" s="3"/>
       <c r="G31" s="4" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>90</v>
+        <v>167</v>
       </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
+      <c r="L31" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M31" s="4" t="s">
+        <v>168</v>
+      </c>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
       <c r="Q31" s="3"/>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>107</v>
+        <v>169</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="4" t="s">
-        <v>107</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="F32" s="3"/>
       <c r="G32" s="4" t="s">
-        <v>32</v>
+        <v>171</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="I32" s="3"/>
+        <v>172</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>173</v>
+      </c>
       <c r="J32" s="3"/>
       <c r="K32" s="3"/>
-      <c r="L32" s="3"/>
-      <c r="M32" s="3"/>
+      <c r="L32" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M32" s="4" t="s">
+        <v>174</v>
+      </c>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
       <c r="Q32" s="3"/>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>109</v>
+        <v>175</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="4" t="s">
-        <v>109</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="F33" s="3"/>
       <c r="G33" s="4" t="s">
-        <v>32</v>
+        <v>179</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
-      <c r="L33" s="3"/>
-      <c r="M33" s="3"/>
+      <c r="L33" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M33" s="4" t="s">
+        <v>181</v>
+      </c>
       <c r="N33" s="3"/>
       <c r="O33" s="3"/>
       <c r="P33" s="3"/>
       <c r="Q33" s="3"/>
     </row>
-    <row r="34" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>111</v>
+        <v>182</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
+        <v>183</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>185</v>
+      </c>
       <c r="F34" s="3"/>
       <c r="G34" s="4" t="s">
-        <v>32</v>
+        <v>186</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>113</v>
+        <v>187</v>
       </c>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3"/>
-      <c r="L34" s="3"/>
-      <c r="M34" s="3"/>
+      <c r="L34" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M34" s="4" t="s">
+        <v>188</v>
+      </c>
       <c r="N34" s="3"/>
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
       <c r="Q34" s="3"/>
     </row>
-    <row r="35" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>63</v>
+        <v>189</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>114</v>
+        <v>190</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>116</v>
+        <v>191</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="4" t="s">
-        <v>117</v>
+        <v>192</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>118</v>
+        <v>193</v>
       </c>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
       <c r="K35" s="3"/>
       <c r="L35" s="4" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="M35" s="4" t="s">
-        <v>119</v>
+        <v>194</v>
       </c>
       <c r="N35" s="3"/>
       <c r="O35" s="3"/>
       <c r="P35" s="3"/>
       <c r="Q35" s="3"/>
     </row>
-    <row r="36" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>1</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>59</v>
+        <v>195</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>120</v>
+        <v>196</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>115</v>
+        <v>184</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>116</v>
+        <v>197</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="4" t="s">
-        <v>117</v>
+        <v>198</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>118</v>
+        <v>187</v>
       </c>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
       <c r="K36" s="3"/>
       <c r="L36" s="4" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="M36" s="4" t="s">
-        <v>119</v>
+        <v>199</v>
       </c>
       <c r="N36" s="3"/>
       <c r="O36" s="3"/>
       <c r="P36" s="3"/>
       <c r="Q36" s="3"/>
     </row>
-    <row r="37" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" ht="105" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>1</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>121</v>
+        <v>200</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>122</v>
+        <v>201</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>116</v>
+        <v>202</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="4" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>118</v>
+        <v>204</v>
       </c>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
       <c r="K37" s="3"/>
       <c r="L37" s="4" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="M37" s="4" t="s">
-        <v>119</v>
+        <v>205</v>
       </c>
       <c r="N37" s="3"/>
       <c r="O37" s="3"/>
       <c r="P37" s="3"/>
       <c r="Q37" s="3"/>
     </row>
-    <row r="38" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>1</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>123</v>
+        <v>206</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>115</v>
+        <v>208</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="F38" s="3"/>
+        <v>206</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>206</v>
+      </c>
       <c r="G38" s="4" t="s">
-        <v>117</v>
+        <v>209</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>118</v>
+        <v>206</v>
       </c>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
       <c r="K38" s="3"/>
       <c r="L38" s="4" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="M38" s="4" t="s">
-        <v>119</v>
+        <v>210</v>
       </c>
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
       <c r="P38" s="3"/>
       <c r="Q38" s="3"/>
     </row>
-    <row r="39" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>1</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>125</v>
+        <v>211</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>126</v>
+        <v>212</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>115</v>
+        <v>208</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>116</v>
+        <v>213</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="4" t="s">
-        <v>117</v>
+        <v>214</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>118</v>
+        <v>213</v>
       </c>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="4" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="M39" s="4" t="s">
-        <v>119</v>
+        <v>215</v>
       </c>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
     </row>
-    <row r="40" spans="1:17" ht="45" x14ac:dyDescent="0.25">
-      <c r="A40" s="3">
-        <v>1</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="F40" s="3"/>
-      <c r="G40" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
-      <c r="K40" s="3"/>
-      <c r="L40" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="M40" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="N40" s="3"/>
-      <c r="O40" s="3"/>
-      <c r="P40" s="3"/>
-      <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="1:17" ht="45" x14ac:dyDescent="0.25">
-      <c r="A41" s="3">
-        <v>1</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="F41" s="3"/>
-      <c r="G41" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="I41" s="3"/>
-      <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="M41" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="N41" s="3"/>
-      <c r="O41" s="3"/>
-      <c r="P41" s="3"/>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="1:17" ht="45" x14ac:dyDescent="0.25">
-      <c r="A42" s="3">
-        <v>1</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="F42" s="3"/>
-      <c r="G42" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
-      <c r="L42" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="M42" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="N42" s="3"/>
-      <c r="O42" s="3"/>
-      <c r="P42" s="3"/>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="1:17" ht="45" x14ac:dyDescent="0.25">
-      <c r="A43" s="3">
-        <v>1</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="F43" s="3"/>
-      <c r="G43" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="I43" s="3"/>
-      <c r="J43" s="3"/>
-      <c r="K43" s="3"/>
-      <c r="L43" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="M43" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="N43" s="3"/>
-      <c r="O43" s="3"/>
-      <c r="P43" s="3"/>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="1:17" ht="45" x14ac:dyDescent="0.25">
-      <c r="A44" s="3">
-        <v>1</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="F44" s="3"/>
-      <c r="G44" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="I44" s="3"/>
-      <c r="J44" s="3"/>
-      <c r="K44" s="3"/>
-      <c r="L44" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="M44" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="N44" s="3"/>
-      <c r="O44" s="3"/>
-      <c r="P44" s="3"/>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="1:17" ht="45" x14ac:dyDescent="0.25">
-      <c r="A45" s="3">
-        <v>1</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="F45" s="3"/>
-      <c r="G45" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="I45" s="3"/>
-      <c r="J45" s="3"/>
-      <c r="K45" s="3"/>
-      <c r="L45" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="M45" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="N45" s="3"/>
-      <c r="O45" s="3"/>
-      <c r="P45" s="3"/>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="1:17" ht="45" x14ac:dyDescent="0.25">
-      <c r="A46" s="3">
-        <v>1</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="F46" s="3"/>
-      <c r="G46" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H46" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="I46" s="3"/>
-      <c r="J46" s="3"/>
-      <c r="K46" s="3"/>
-      <c r="L46" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="M46" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="N46" s="3"/>
-      <c r="O46" s="3"/>
-      <c r="P46" s="3"/>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="1:17" ht="45" x14ac:dyDescent="0.25">
-      <c r="A47" s="3">
-        <v>1</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="F47" s="3"/>
-      <c r="G47" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H47" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="I47" s="3"/>
-      <c r="J47" s="3"/>
-      <c r="K47" s="3"/>
-      <c r="L47" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="M47" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="N47" s="3"/>
-      <c r="O47" s="3"/>
-      <c r="P47" s="3"/>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="1:17" ht="60" x14ac:dyDescent="0.25">
-      <c r="A48" s="3">
-        <v>8</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="F48" s="3"/>
-      <c r="G48" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="H48" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="I48" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="J48" s="3"/>
-      <c r="K48" s="3"/>
-      <c r="L48" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="M48" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="N48" s="3"/>
-      <c r="O48" s="3"/>
-      <c r="P48" s="3"/>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="1:17" ht="30" x14ac:dyDescent="0.25">
-      <c r="A49" s="3">
-        <v>4</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="H49" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="I49" s="3"/>
-      <c r="J49" s="3"/>
-      <c r="K49" s="3"/>
-      <c r="L49" s="3"/>
-      <c r="M49" s="3"/>
-      <c r="N49" s="3"/>
-      <c r="O49" s="3"/>
-      <c r="P49" s="3"/>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="1:17" ht="60" x14ac:dyDescent="0.25">
-      <c r="A50" s="3">
-        <v>1</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="F50" s="3"/>
-      <c r="G50" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="H50" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="I50" s="3"/>
-      <c r="J50" s="3"/>
-      <c r="K50" s="3"/>
-      <c r="L50" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="M50" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="N50" s="3"/>
-      <c r="O50" s="3"/>
-      <c r="P50" s="3"/>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A51" s="3">
-        <v>3</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="F51" s="3"/>
-      <c r="G51" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="H51" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="I51" s="3"/>
-      <c r="J51" s="3"/>
-      <c r="K51" s="3"/>
-      <c r="L51" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="M51" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="N51" s="3"/>
-      <c r="O51" s="3"/>
-      <c r="P51" s="3"/>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="1:17" ht="60" x14ac:dyDescent="0.25">
-      <c r="A52" s="3">
-        <v>1</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F52" s="3"/>
-      <c r="G52" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="H52" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="I52" s="3"/>
-      <c r="J52" s="3"/>
-      <c r="K52" s="3"/>
-      <c r="L52" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="M52" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="N52" s="3"/>
-      <c r="O52" s="3"/>
-      <c r="P52" s="3"/>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="1:17" ht="105" x14ac:dyDescent="0.25">
-      <c r="A53" s="3">
-        <v>1</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="F53" s="3"/>
-      <c r="G53" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="H53" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="I53" s="3"/>
-      <c r="J53" s="3"/>
-      <c r="K53" s="3"/>
-      <c r="L53" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="M53" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="N53" s="3"/>
-      <c r="O53" s="3"/>
-      <c r="P53" s="3"/>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="1:17" ht="75" x14ac:dyDescent="0.25">
-      <c r="A54" s="3">
-        <v>1</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="D54" s="3"/>
-      <c r="E54" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="H54" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="I54" s="3"/>
-      <c r="J54" s="3"/>
-      <c r="K54" s="3"/>
-      <c r="L54" s="3"/>
-      <c r="M54" s="3"/>
-      <c r="N54" s="3"/>
-      <c r="O54" s="3"/>
-      <c r="P54" s="3"/>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="1:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="A55" s="3">
-        <v>1</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="F55" s="3"/>
-      <c r="G55" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="H55" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="I55" s="3"/>
-      <c r="J55" s="3"/>
-      <c r="K55" s="3"/>
-      <c r="L55" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="M55" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="N55" s="3"/>
-      <c r="O55" s="3"/>
-      <c r="P55" s="3"/>
-      <c r="Q55" s="3"/>
-    </row>
   </sheetData>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.30555555555555558" right="0.30555555555555558" top="0.30555555555555558" bottom="0.30555555555555558" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="14" orientation="landscape" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="16" orientation="landscape" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>